--- a/Phase 1 Design, Kinematics & Core Theory (The Digital Foundation)/1 Conceptual Design & CAD/Bill Of Materials.xlsx
+++ b/Phase 1 Design, Kinematics & Core Theory (The Digital Foundation)/1 Conceptual Design & CAD/Bill Of Materials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Engineering\Robotics\Kuka Project\GIthub_Repos\Phase 1 Design, Kinematics &amp; Core Theory (The Digital Foundation)\1 Conceptual Design &amp; CAD\Solidwork FIles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Engineering\Robotics\Kuka Project\GIthub_Repos\Phase 1 Design, Kinematics &amp; Core Theory (The Digital Foundation)\1 Conceptual Design &amp; CAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7722623-6C02-4C3E-B44E-FCC30BE3858A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5247EB8-405E-4891-A603-40E4743A0651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="3d parts" sheetId="1" r:id="rId1"/>
@@ -838,7 +838,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -937,24 +937,55 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -991,12 +1022,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1007,46 +1044,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1339,10 +1336,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="37"/>
+      <c r="B1" s="50"/>
       <c r="C1" s="14" t="s">
         <v>3</v>
       </c>
@@ -1357,10 +1354,10 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="55" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1371,8 +1368,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="39"/>
-      <c r="B3" s="45"/>
+      <c r="A3" s="43"/>
+      <c r="B3" s="56"/>
       <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1381,8 +1378,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="39"/>
-      <c r="B4" s="45"/>
+      <c r="A4" s="43"/>
+      <c r="B4" s="56"/>
       <c r="C4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1391,7 +1388,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="40"/>
+      <c r="A5" s="51"/>
       <c r="B5" s="6" t="s">
         <v>12</v>
       </c>
@@ -1412,10 +1409,10 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="41" t="s">
+      <c r="A6" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="57" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="8" t="s">
@@ -1426,8 +1423,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="42"/>
-      <c r="B7" s="47"/>
+      <c r="A7" s="53"/>
+      <c r="B7" s="58"/>
       <c r="C7" s="10" t="s">
         <v>10</v>
       </c>
@@ -1436,8 +1433,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="42"/>
-      <c r="B8" s="47"/>
+      <c r="A8" s="53"/>
+      <c r="B8" s="58"/>
       <c r="C8" s="10" t="s">
         <v>11</v>
       </c>
@@ -1446,8 +1443,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="42"/>
-      <c r="B9" s="48"/>
+      <c r="A9" s="53"/>
+      <c r="B9" s="59"/>
       <c r="C9" s="10" t="s">
         <v>13</v>
       </c>
@@ -1456,8 +1453,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="42"/>
-      <c r="B10" s="49" t="s">
+      <c r="A10" s="53"/>
+      <c r="B10" s="60" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="10" t="s">
@@ -1468,8 +1465,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="42"/>
-      <c r="B11" s="47"/>
+      <c r="A11" s="53"/>
+      <c r="B11" s="58"/>
       <c r="C11" s="32" t="s">
         <v>8</v>
       </c>
@@ -1487,8 +1484,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="43"/>
-      <c r="B12" s="50"/>
+      <c r="A12" s="54"/>
+      <c r="B12" s="61"/>
       <c r="C12" s="12" t="s">
         <v>23</v>
       </c>
@@ -1506,10 +1503,10 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="38" t="s">
+      <c r="A13" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="62" t="s">
         <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -1520,8 +1517,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="39"/>
-      <c r="B14" s="52"/>
+      <c r="A14" s="43"/>
+      <c r="B14" s="41"/>
       <c r="C14" s="4" t="s">
         <v>17</v>
       </c>
@@ -1530,8 +1527,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="39"/>
-      <c r="B15" s="52"/>
+      <c r="A15" s="43"/>
+      <c r="B15" s="41"/>
       <c r="C15" s="4" t="s">
         <v>18</v>
       </c>
@@ -1540,8 +1537,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="39"/>
-      <c r="B16" s="52"/>
+      <c r="A16" s="43"/>
+      <c r="B16" s="41"/>
       <c r="C16" s="4" t="s">
         <v>19</v>
       </c>
@@ -1550,8 +1547,8 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="39"/>
-      <c r="B17" s="34" t="s">
+      <c r="A17" s="43"/>
+      <c r="B17" s="46" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="4" t="s">
@@ -1562,8 +1559,8 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="39"/>
-      <c r="B18" s="52"/>
+      <c r="A18" s="43"/>
+      <c r="B18" s="41"/>
       <c r="C18" s="4" t="s">
         <v>22</v>
       </c>
@@ -1572,8 +1569,8 @@
       </c>
     </row>
     <row r="19" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="40"/>
-      <c r="B19" s="53"/>
+      <c r="A19" s="51"/>
+      <c r="B19" s="63"/>
       <c r="C19" s="31" t="s">
         <v>8</v>
       </c>
@@ -1591,7 +1588,7 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="63" t="s">
+      <c r="A20" s="48" t="s">
         <v>43</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -1605,8 +1602,8 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="61"/>
-      <c r="B21" s="34" t="s">
+      <c r="A21" s="49"/>
+      <c r="B21" s="46" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="4" t="s">
@@ -1617,8 +1614,8 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="61"/>
-      <c r="B22" s="35"/>
+      <c r="A22" s="49"/>
+      <c r="B22" s="47"/>
       <c r="C22" s="32" t="s">
         <v>89</v>
       </c>
@@ -1636,7 +1633,7 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="38" t="s">
+      <c r="A23" s="42" t="s">
         <v>48</v>
       </c>
       <c r="B23" s="30" t="s">
@@ -1650,8 +1647,8 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="39"/>
-      <c r="B24" s="52" t="s">
+      <c r="A24" s="43"/>
+      <c r="B24" s="41" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="4" t="s">
@@ -1662,8 +1659,8 @@
       </c>
     </row>
     <row r="25" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A25" s="39"/>
-      <c r="B25" s="52"/>
+      <c r="A25" s="43"/>
+      <c r="B25" s="41"/>
       <c r="C25" s="4" t="s">
         <v>102</v>
       </c>
@@ -1681,21 +1678,21 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="68" t="s">
+      <c r="A26" s="44" t="s">
         <v>47</v>
       </c>
       <c r="B26" t="s">
         <v>1</v>
       </c>
-      <c r="C26" s="64" t="s">
+      <c r="C26" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="D26" s="65">
+      <c r="D26" s="36">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="36"/>
+      <c r="A27" s="45"/>
       <c r="B27" t="s">
         <v>12</v>
       </c>
@@ -1722,28 +1719,23 @@
       <c r="B28" t="s">
         <v>1</v>
       </c>
-      <c r="C28" s="64" t="s">
+      <c r="C28" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="D28" s="65">
+      <c r="D28" s="36">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C29" s="70" t="s">
+      <c r="C29" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D29" s="70">
+      <c r="D29" s="1">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="A20:A22"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A13:A19"/>
     <mergeCell ref="A2:A5"/>
@@ -1753,6 +1745,11 @@
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="B13:B16"/>
     <mergeCell ref="B17:B19"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="A20:A22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F5" r:id="rId1" xr:uid="{B5095CBD-914B-4D63-BA4A-A2C5AFDF70A8}"/>
@@ -1818,17 +1815,17 @@
       <c r="H2" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="37" t="s">
+      <c r="I2" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37" t="s">
+      <c r="J2" s="50"/>
+      <c r="K2" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="37"/>
+      <c r="L2" s="50"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="50" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="19" t="s">
@@ -1866,7 +1863,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="37"/>
+      <c r="A4" s="50"/>
       <c r="B4" s="20" t="s">
         <v>31</v>
       </c>
@@ -1902,7 +1899,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="66" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="21" t="s">
@@ -1940,7 +1937,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="60"/>
+      <c r="A6" s="66"/>
       <c r="B6" s="22" t="s">
         <v>31</v>
       </c>
@@ -1972,7 +1969,7 @@
       <c r="L6" s="11"/>
     </row>
     <row r="7" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="60"/>
+      <c r="A7" s="66"/>
       <c r="B7" s="22" t="s">
         <v>35</v>
       </c>
@@ -2004,7 +2001,7 @@
       <c r="L7" s="11"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="60"/>
+      <c r="A8" s="66"/>
       <c r="B8" s="23" t="s">
         <v>39</v>
       </c>
@@ -2026,14 +2023,14 @@
       <c r="H8" s="12">
         <v>5</v>
       </c>
-      <c r="I8" s="58" t="s">
+      <c r="I8" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="J8" s="58"/>
-      <c r="K8" s="58" t="s">
+      <c r="J8" s="64"/>
+      <c r="K8" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="L8" s="59"/>
+      <c r="L8" s="65"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
@@ -2094,15 +2091,15 @@
       <c r="H10" s="8">
         <v>9</v>
       </c>
-      <c r="I10" s="55" t="s">
+      <c r="I10" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="J10" s="55"/>
+      <c r="J10" s="68"/>
       <c r="K10" s="8"/>
       <c r="L10" s="9"/>
     </row>
     <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="66" t="s">
+      <c r="A11" s="37" t="s">
         <v>48</v>
       </c>
       <c r="B11" s="20" t="s">
@@ -2126,15 +2123,15 @@
       <c r="H11" s="6">
         <v>5</v>
       </c>
-      <c r="I11" s="54" t="s">
+      <c r="I11" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="J11" s="54"/>
+      <c r="J11" s="67"/>
       <c r="K11" s="6"/>
       <c r="L11" s="7"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="38" t="s">
         <v>47</v>
       </c>
       <c r="B12" s="18" t="s">
@@ -2158,14 +2155,14 @@
       <c r="H12" s="17">
         <v>5</v>
       </c>
-      <c r="I12" s="56" t="s">
+      <c r="I12" s="69" t="s">
         <v>46</v>
       </c>
-      <c r="J12" s="57"/>
-      <c r="K12" s="56" t="s">
+      <c r="J12" s="70"/>
+      <c r="K12" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="L12" s="57"/>
+      <c r="L12" s="70"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="25"/>
@@ -3241,16 +3238,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="K8:L8"/>
     <mergeCell ref="A5:A8"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="55" orientation="portrait" r:id="rId1"/>
@@ -3302,10 +3299,10 @@
       <c r="B3" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="69" t="s">
+      <c r="C3" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="69" t="s">
+      <c r="D3" s="39" t="s">
         <v>85</v>
       </c>
       <c r="H3" t="s">
@@ -3396,10 +3393,10 @@
       <c r="B8" t="s">
         <v>83</v>
       </c>
-      <c r="C8" s="69" t="s">
+      <c r="C8" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="D8" s="69" t="s">
+      <c r="D8" s="39" t="s">
         <v>113</v>
       </c>
     </row>
@@ -3461,10 +3458,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="49" t="s">
         <v>59</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -3478,8 +3475,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="61"/>
-      <c r="B3" s="61"/>
+      <c r="A3" s="49"/>
+      <c r="B3" s="49"/>
       <c r="C3" s="1" t="s">
         <v>62</v>
       </c>
@@ -3491,7 +3488,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="61"/>
+      <c r="A4" s="49"/>
       <c r="B4" s="1" t="s">
         <v>58</v>
       </c>
@@ -3503,10 +3500,10 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="61" t="s">
+      <c r="A5" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="61" t="s">
+      <c r="B5" s="49" t="s">
         <v>59</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -3520,8 +3517,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="61"/>
-      <c r="B6" s="61"/>
+      <c r="A6" s="49"/>
+      <c r="B6" s="49"/>
       <c r="C6" s="1" t="s">
         <v>61</v>
       </c>
@@ -3533,8 +3530,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="61"/>
-      <c r="B7" s="61"/>
+      <c r="A7" s="49"/>
+      <c r="B7" s="49"/>
       <c r="C7" s="1" t="s">
         <v>61</v>
       </c>
@@ -3549,8 +3546,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="61"/>
-      <c r="B8" s="61"/>
+      <c r="A8" s="49"/>
+      <c r="B8" s="49"/>
       <c r="C8" s="1" t="s">
         <v>77</v>
       </c>
@@ -3562,8 +3559,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="61"/>
-      <c r="B9" s="61"/>
+      <c r="A9" s="49"/>
+      <c r="B9" s="49"/>
       <c r="C9" s="1" t="s">
         <v>62</v>
       </c>
@@ -3575,8 +3572,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="61"/>
-      <c r="B10" s="61" t="s">
+      <c r="A10" s="49"/>
+      <c r="B10" s="49" t="s">
         <v>58</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -3587,8 +3584,8 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="61"/>
-      <c r="B11" s="61"/>
+      <c r="A11" s="49"/>
+      <c r="B11" s="49"/>
       <c r="C11" s="1" t="s">
         <v>77</v>
       </c>
@@ -3600,10 +3597,10 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="61" t="s">
+      <c r="A12" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="61" t="s">
+      <c r="B12" s="49" t="s">
         <v>59</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -3617,8 +3614,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="61"/>
-      <c r="B13" s="61"/>
+      <c r="A13" s="49"/>
+      <c r="B13" s="49"/>
       <c r="C13" s="1" t="s">
         <v>62</v>
       </c>
@@ -3630,7 +3627,7 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="61"/>
+      <c r="A14" s="49"/>
       <c r="B14" s="1" t="s">
         <v>58</v>
       </c>
@@ -3642,10 +3639,10 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="49" t="s">
         <v>90</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -3662,6 +3659,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="49"/>
+      <c r="B16" s="49"/>
       <c r="C16" s="1" t="s">
         <v>77</v>
       </c>
@@ -3673,6 +3672,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="49"/>
+      <c r="B17" s="49"/>
       <c r="C17" s="1" t="s">
         <v>62</v>
       </c>
@@ -3684,10 +3685,10 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="49" t="s">
         <v>59</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -3701,6 +3702,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="49"/>
+      <c r="B19" s="49"/>
       <c r="C19" s="1" t="s">
         <v>109</v>
       </c>
@@ -3712,7 +3715,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="1" t="s">
+      <c r="A20" s="49"/>
+      <c r="B20" s="49" t="s">
         <v>58</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -3723,6 +3727,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="49"/>
+      <c r="B21" s="49"/>
       <c r="C21" s="1" t="s">
         <v>109</v>
       </c>
@@ -3751,7 +3757,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="12">
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B20:B21"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="A2:A4"/>
@@ -3772,7 +3783,7 @@
     <col min="1" max="1" width="15.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="8" width="15.7109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="3.85546875" style="71" customWidth="1"/>
+    <col min="9" max="9" width="3.85546875" style="40" customWidth="1"/>
     <col min="10" max="11" width="9.140625" style="1"/>
     <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" style="1" bestFit="1" customWidth="1"/>
@@ -3782,68 +3793,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="61" t="s">
+      <c r="C1" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61" t="s">
+      <c r="D1" s="49"/>
+      <c r="E1" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="F1" s="61" t="s">
+      <c r="F1" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="G1" s="61" t="s">
+      <c r="G1" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="H1" s="61" t="s">
+      <c r="H1" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="J1" s="61" t="s">
+      <c r="J1" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61" t="s">
+      <c r="K1" s="49"/>
+      <c r="L1" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="M1" s="61" t="s">
+      <c r="M1" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="N1" s="61" t="s">
+      <c r="N1" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="O1" s="61" t="s">
+      <c r="O1" s="49" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="61"/>
-      <c r="B2" s="61"/>
+      <c r="A2" s="49"/>
+      <c r="B2" s="49"/>
       <c r="C2" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
       <c r="J2" s="1" t="s">
         <v>68</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="49"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -3948,20 +3959,20 @@
       <c r="H6" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="J6" s="62">
+      <c r="J6" s="35">
         <v>20</v>
       </c>
-      <c r="K6" s="62">
+      <c r="K6" s="35">
         <v>32.200000000000003</v>
       </c>
-      <c r="L6" s="62">
+      <c r="L6" s="35">
         <v>5</v>
       </c>
-      <c r="M6" s="62">
+      <c r="M6" s="35">
         <v>10.5</v>
       </c>
-      <c r="N6" s="62"/>
-      <c r="O6" s="62"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="35"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -4017,18 +4028,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="F1:F2"/>
     <mergeCell ref="L1:L2"/>
     <mergeCell ref="M1:M2"/>
     <mergeCell ref="N1:N2"/>
     <mergeCell ref="O1:O2"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="J1:K1"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="F1:F2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" xr:uid="{D40B1BD2-F826-4A33-8F0F-ACB54534C7E7}"/>

--- a/Phase 1 Design, Kinematics & Core Theory (The Digital Foundation)/1 Conceptual Design & CAD/Bill Of Materials.xlsx
+++ b/Phase 1 Design, Kinematics & Core Theory (The Digital Foundation)/1 Conceptual Design & CAD/Bill Of Materials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Engineering\Robotics\Kuka Project\GIthub_Repos\Phase 1 Design, Kinematics &amp; Core Theory (The Digital Foundation)\1 Conceptual Design &amp; CAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5247EB8-405E-4891-A603-40E4743A0651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19AC9797-696B-459B-ABD5-FB1AC9FAFE43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="3d parts" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="125">
   <si>
     <t>Joint 01</t>
   </si>
@@ -409,6 +409,12 @@
   </si>
   <si>
     <t>NEMA 08</t>
+  </si>
+  <si>
+    <t>Mass</t>
+  </si>
+  <si>
+    <t>Calculated oin the idler</t>
   </si>
 </sst>
 </file>
@@ -838,7 +844,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -956,13 +962,61 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
@@ -971,58 +1025,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1034,16 +1052,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1327,37 +1339,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" customWidth="1"/>
-    <col min="7" max="7" width="46.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" customWidth="1"/>
+    <col min="8" max="8" width="46.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="50"/>
+      <c r="B1" s="42"/>
       <c r="C1" s="14" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="71" t="s">
+        <v>123</v>
+      </c>
+      <c r="F1" t="s">
         <v>53</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="49" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1366,29 +1381,38 @@
       <c r="D2" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="43"/>
-      <c r="B3" s="56"/>
+      <c r="E2" s="71">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="44"/>
+      <c r="B3" s="50"/>
       <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="43"/>
-      <c r="B4" s="56"/>
+      <c r="E3" s="71">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="44"/>
+      <c r="B4" s="50"/>
       <c r="C4" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="51"/>
+      <c r="E4" s="71">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="45"/>
       <c r="B5" s="6" t="s">
         <v>12</v>
       </c>
@@ -1398,21 +1422,24 @@
       <c r="D5" s="7">
         <v>1</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="71">
+        <v>5.5</v>
+      </c>
+      <c r="F5" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="G5" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="52" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="57" t="s">
+      <c r="B6" s="51" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="8" t="s">
@@ -1421,40 +1448,52 @@
       <c r="D6" s="9">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="53"/>
-      <c r="B7" s="58"/>
+      <c r="E6" s="72">
+        <v>252.88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="47"/>
+      <c r="B7" s="52"/>
       <c r="C7" s="10" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="53"/>
-      <c r="B8" s="58"/>
+      <c r="E7" s="72">
+        <v>27.07</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="47"/>
+      <c r="B8" s="52"/>
       <c r="C8" s="10" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="53"/>
-      <c r="B9" s="59"/>
+      <c r="E8" s="72">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="47"/>
+      <c r="B9" s="53"/>
       <c r="C9" s="10" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="53"/>
-      <c r="B10" s="60" t="s">
+      <c r="E9" s="72">
+        <v>8.48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="47"/>
+      <c r="B10" s="54" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="10" t="s">
@@ -1463,50 +1502,57 @@
       <c r="D10" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="53"/>
-      <c r="B11" s="58"/>
+      <c r="E10" s="72"/>
+    </row>
+    <row r="11" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="47"/>
+      <c r="B11" s="52"/>
       <c r="C11" s="32" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="11">
         <v>1</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="72">
+        <v>5.5</v>
+      </c>
+      <c r="F11" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="27" t="s">
+      <c r="G11" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="54"/>
-      <c r="B12" s="61"/>
+    <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="48"/>
+      <c r="B12" s="55"/>
       <c r="C12" s="12" t="s">
         <v>23</v>
       </c>
       <c r="D12" s="13">
         <v>1</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="72">
+        <v>21.6</v>
+      </c>
+      <c r="F12" t="s">
         <v>73</v>
       </c>
-      <c r="F12" s="28" t="s">
+      <c r="G12" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="42" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="62" t="s">
+      <c r="B13" s="56" t="s">
         <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -1515,40 +1561,44 @@
       <c r="D13" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="43"/>
-      <c r="B14" s="41"/>
+      <c r="E13" s="71"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="44"/>
+      <c r="B14" s="57"/>
       <c r="C14" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D14" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="43"/>
-      <c r="B15" s="41"/>
+      <c r="E14" s="71"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="44"/>
+      <c r="B15" s="57"/>
       <c r="C15" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D15" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="43"/>
-      <c r="B16" s="41"/>
+      <c r="E15" s="71"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="44"/>
+      <c r="B16" s="57"/>
       <c r="C16" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D16" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="43"/>
-      <c r="B17" s="46" t="s">
+      <c r="E16" s="71"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="44"/>
+      <c r="B17" s="58" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="4" t="s">
@@ -1557,38 +1607,41 @@
       <c r="D17" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="43"/>
-      <c r="B18" s="41"/>
+      <c r="E17" s="71"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="44"/>
+      <c r="B18" s="57"/>
       <c r="C18" s="4" t="s">
         <v>22</v>
       </c>
       <c r="D18" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="51"/>
-      <c r="B19" s="63"/>
+      <c r="E18" s="71"/>
+    </row>
+    <row r="19" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="45"/>
+      <c r="B19" s="59"/>
       <c r="C19" s="31" t="s">
         <v>8</v>
       </c>
       <c r="D19" s="7">
         <v>1</v>
       </c>
-      <c r="E19" s="26" t="s">
+      <c r="E19" s="71"/>
+      <c r="F19" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F19" s="27" t="s">
+      <c r="G19" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="48" t="s">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="63" t="s">
         <v>43</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -1600,10 +1653,11 @@
       <c r="D20" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="49"/>
-      <c r="B21" s="46" t="s">
+      <c r="E20" s="71"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="41"/>
+      <c r="B21" s="58" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="4" t="s">
@@ -1612,28 +1666,30 @@
       <c r="D21" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="49"/>
-      <c r="B22" s="47"/>
+      <c r="E21" s="71"/>
+    </row>
+    <row r="22" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="41"/>
+      <c r="B22" s="62"/>
       <c r="C22" s="32" t="s">
         <v>89</v>
       </c>
       <c r="D22" s="5">
         <v>1</v>
       </c>
-      <c r="E22" s="26" t="s">
+      <c r="E22" s="71"/>
+      <c r="F22" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F22" s="27" t="s">
+      <c r="G22" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="42" t="s">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="43" t="s">
         <v>48</v>
       </c>
       <c r="B23" s="30" t="s">
@@ -1645,10 +1701,11 @@
       <c r="D23" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="43"/>
-      <c r="B24" s="41" t="s">
+      <c r="E23" s="71"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="44"/>
+      <c r="B24" s="57" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="4" t="s">
@@ -1657,28 +1714,30 @@
       <c r="D24" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A25" s="43"/>
-      <c r="B25" s="41"/>
+      <c r="E24" s="71"/>
+    </row>
+    <row r="25" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="44"/>
+      <c r="B25" s="57"/>
       <c r="C25" s="4" t="s">
         <v>102</v>
       </c>
       <c r="D25" s="5">
         <v>1</v>
       </c>
-      <c r="E25" s="26" t="s">
+      <c r="E25" s="71"/>
+      <c r="F25" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F25" s="27" t="s">
+      <c r="G25" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="44" t="s">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="60" t="s">
         <v>47</v>
       </c>
       <c r="B26" t="s">
@@ -1690,9 +1749,10 @@
       <c r="D26" s="36">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="45"/>
+      <c r="E26" s="71"/>
+    </row>
+    <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="61"/>
       <c r="B27" t="s">
         <v>12</v>
       </c>
@@ -1702,17 +1762,18 @@
       <c r="D27" s="13">
         <v>2</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="72"/>
+      <c r="F27" t="s">
         <v>73</v>
       </c>
-      <c r="F27" s="28" t="s">
+      <c r="G27" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>114</v>
       </c>
@@ -1725,17 +1786,24 @@
       <c r="D28" s="36">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E28" s="71"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C29" s="1" t="s">
         <v>116</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
       </c>
+      <c r="E29" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="A20:A22"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A13:A19"/>
     <mergeCell ref="A2:A5"/>
@@ -1745,20 +1813,15 @@
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="B13:B16"/>
     <mergeCell ref="B17:B19"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="A20:A22"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F5" r:id="rId1" xr:uid="{B5095CBD-914B-4D63-BA4A-A2C5AFDF70A8}"/>
-    <hyperlink ref="F12" r:id="rId2" xr:uid="{BFB782D1-5E1B-411B-9604-669FC0236F16}"/>
-    <hyperlink ref="F19" r:id="rId3" xr:uid="{22D12652-0DAC-4555-B5B2-3D08F290EBA8}"/>
-    <hyperlink ref="F11" r:id="rId4" xr:uid="{B8CDC57B-9589-4E49-8A24-F64059F604C7}"/>
-    <hyperlink ref="F22" r:id="rId5" xr:uid="{57F689DF-395D-48AA-BF84-FB717739049F}"/>
-    <hyperlink ref="F25" r:id="rId6" xr:uid="{9E87D0CC-0808-4028-A359-09AC3A206762}"/>
-    <hyperlink ref="F27" r:id="rId7" xr:uid="{2AEEE6F8-83B2-4B34-9795-76910E13B16D}"/>
+    <hyperlink ref="G5" r:id="rId1" xr:uid="{B5095CBD-914B-4D63-BA4A-A2C5AFDF70A8}"/>
+    <hyperlink ref="G12" r:id="rId2" xr:uid="{BFB782D1-5E1B-411B-9604-669FC0236F16}"/>
+    <hyperlink ref="G19" r:id="rId3" xr:uid="{22D12652-0DAC-4555-B5B2-3D08F290EBA8}"/>
+    <hyperlink ref="G11" r:id="rId4" xr:uid="{B8CDC57B-9589-4E49-8A24-F64059F604C7}"/>
+    <hyperlink ref="G22" r:id="rId5" xr:uid="{57F689DF-395D-48AA-BF84-FB717739049F}"/>
+    <hyperlink ref="G25" r:id="rId6" xr:uid="{9E87D0CC-0808-4028-A359-09AC3A206762}"/>
+    <hyperlink ref="G27" r:id="rId7" xr:uid="{2AEEE6F8-83B2-4B34-9795-76910E13B16D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1766,17 +1829,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42527CE2-A18A-49C8-858C-36F840735889}">
-  <dimension ref="A1:L83"/>
+  <dimension ref="A1:N83"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="3" width="20.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="8" width="9.140625" style="1"/>
     <col min="9" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="13" max="13" width="9.140625" style="1"/>
+    <col min="14" max="14" width="22" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="25"/>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -1790,7 +1855,7 @@
       <c r="K1" s="25"/>
       <c r="L1" s="25"/>
     </row>
-    <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>24</v>
       </c>
@@ -1815,17 +1880,20 @@
       <c r="H2" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="50" t="s">
+      <c r="I2" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50" t="s">
+      <c r="J2" s="42"/>
+      <c r="K2" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="50"/>
-    </row>
-    <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="50" t="s">
+      <c r="L2" s="42"/>
+      <c r="M2" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="42" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="19" t="s">
@@ -1861,9 +1929,12 @@
       <c r="L3" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="50"/>
+      <c r="M3" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="42"/>
       <c r="B4" s="20" t="s">
         <v>31</v>
       </c>
@@ -1897,9 +1968,12 @@
       <c r="L4" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="66" t="s">
+      <c r="M4" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="70" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="21" t="s">
@@ -1935,9 +2009,12 @@
       <c r="L5" s="9" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="66"/>
+      <c r="M5" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="70"/>
       <c r="B6" s="22" t="s">
         <v>31</v>
       </c>
@@ -1967,9 +2044,12 @@
       </c>
       <c r="K6" s="10"/>
       <c r="L6" s="11"/>
-    </row>
-    <row r="7" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="66"/>
+      <c r="M6" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="70"/>
       <c r="B7" s="22" t="s">
         <v>35</v>
       </c>
@@ -1999,9 +2079,12 @@
       </c>
       <c r="K7" s="10"/>
       <c r="L7" s="11"/>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="66"/>
+      <c r="M7" s="1">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="70"/>
       <c r="B8" s="23" t="s">
         <v>39</v>
       </c>
@@ -2023,16 +2106,22 @@
       <c r="H8" s="12">
         <v>5</v>
       </c>
-      <c r="I8" s="64" t="s">
+      <c r="I8" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="J8" s="64"/>
-      <c r="K8" s="64" t="s">
+      <c r="J8" s="68"/>
+      <c r="K8" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="L8" s="65"/>
-    </row>
-    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L8" s="69"/>
+      <c r="M8" s="1">
+        <v>5</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>15</v>
       </c>
@@ -2065,8 +2154,11 @@
       </c>
       <c r="K9" s="15"/>
       <c r="L9" s="16"/>
-    </row>
-    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M9" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="33" t="s">
         <v>43</v>
       </c>
@@ -2091,14 +2183,17 @@
       <c r="H10" s="8">
         <v>9</v>
       </c>
-      <c r="I10" s="68" t="s">
+      <c r="I10" s="65" t="s">
         <v>45</v>
       </c>
-      <c r="J10" s="68"/>
+      <c r="J10" s="65"/>
       <c r="K10" s="8"/>
       <c r="L10" s="9"/>
-    </row>
-    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M10" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="37" t="s">
         <v>48</v>
       </c>
@@ -2123,14 +2218,14 @@
       <c r="H11" s="6">
         <v>5</v>
       </c>
-      <c r="I11" s="67" t="s">
+      <c r="I11" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="J11" s="67"/>
+      <c r="J11" s="64"/>
       <c r="K11" s="6"/>
       <c r="L11" s="7"/>
     </row>
-    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="38" t="s">
         <v>47</v>
       </c>
@@ -2155,16 +2250,16 @@
       <c r="H12" s="17">
         <v>5</v>
       </c>
-      <c r="I12" s="69" t="s">
+      <c r="I12" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="J12" s="70"/>
-      <c r="K12" s="69" t="s">
+      <c r="J12" s="67"/>
+      <c r="K12" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="L12" s="70"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L12" s="67"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="25"/>
       <c r="B13" s="25"/>
       <c r="C13" s="25"/>
@@ -2181,7 +2276,7 @@
       <c r="K13" s="25"/>
       <c r="L13" s="25"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="25"/>
       <c r="B14" s="25"/>
       <c r="C14" s="25"/>
@@ -2195,7 +2290,7 @@
       <c r="K14" s="25"/>
       <c r="L14" s="25"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="25"/>
       <c r="B15" s="25"/>
       <c r="C15" s="25"/>
@@ -2209,7 +2304,7 @@
       <c r="K15" s="25"/>
       <c r="L15" s="25"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="25"/>
       <c r="B16" s="25"/>
       <c r="C16" s="25"/>
@@ -3238,16 +3333,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="A5:A8"/>
     <mergeCell ref="I11:J11"/>
     <mergeCell ref="I10:J10"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="K12:L12"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="A5:A8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="55" orientation="portrait" r:id="rId1"/>
@@ -3429,15 +3524,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{259DF173-3712-469C-8216-13FC30CB8ABB}">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" width="9.140625" style="1"/>
-    <col min="6" max="6" width="53.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="6" width="9.140625" style="1"/>
+    <col min="7" max="7" width="53.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>24</v>
       </c>
@@ -3454,14 +3549,17 @@
         <v>60</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="49" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="41" t="s">
         <v>59</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -3473,10 +3571,13 @@
       <c r="E2" s="1">
         <v>70</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="49"/>
-      <c r="B3" s="49"/>
+      <c r="F2" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="41"/>
+      <c r="B3" s="41"/>
       <c r="C3" s="1" t="s">
         <v>62</v>
       </c>
@@ -3486,9 +3587,12 @@
       <c r="E3" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="49"/>
+      <c r="F3" s="1">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="41"/>
       <c r="B4" s="1" t="s">
         <v>58</v>
       </c>
@@ -3498,12 +3602,15 @@
       <c r="D4" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="49" t="s">
+      <c r="F4" s="1">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="49" t="s">
+      <c r="B5" s="41" t="s">
         <v>59</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -3516,9 +3623,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="49"/>
-      <c r="B6" s="49"/>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="41"/>
+      <c r="B6" s="41"/>
       <c r="C6" s="1" t="s">
         <v>61</v>
       </c>
@@ -3529,9 +3636,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="49"/>
-      <c r="B7" s="49"/>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="41"/>
+      <c r="B7" s="41"/>
       <c r="C7" s="1" t="s">
         <v>61</v>
       </c>
@@ -3541,13 +3648,13 @@
       <c r="E7" s="1">
         <v>40</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="49"/>
-      <c r="B8" s="49"/>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="41"/>
+      <c r="B8" s="41"/>
       <c r="C8" s="1" t="s">
         <v>77</v>
       </c>
@@ -3558,9 +3665,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="49"/>
-      <c r="B9" s="49"/>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="41"/>
+      <c r="B9" s="41"/>
       <c r="C9" s="1" t="s">
         <v>62</v>
       </c>
@@ -3571,9 +3678,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="49"/>
-      <c r="B10" s="49" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="41"/>
+      <c r="B10" s="41" t="s">
         <v>58</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -3583,24 +3690,24 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="49"/>
-      <c r="B11" s="49"/>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="41"/>
+      <c r="B11" s="41"/>
       <c r="C11" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D11" s="1">
         <v>4</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="49" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="49" t="s">
+      <c r="B12" s="41" t="s">
         <v>59</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -3613,9 +3720,9 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="49"/>
-      <c r="B13" s="49"/>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="41"/>
+      <c r="B13" s="41"/>
       <c r="C13" s="1" t="s">
         <v>62</v>
       </c>
@@ -3626,8 +3733,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="49"/>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="41"/>
       <c r="B14" s="1" t="s">
         <v>58</v>
       </c>
@@ -3638,11 +3745,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="49" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="49" t="s">
+      <c r="B15" s="41" t="s">
         <v>90</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -3654,13 +3761,13 @@
       <c r="E15" s="1">
         <v>80</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="49"/>
-      <c r="B16" s="49"/>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="41"/>
+      <c r="B16" s="41"/>
       <c r="C16" s="1" t="s">
         <v>77</v>
       </c>
@@ -3671,9 +3778,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="49"/>
-      <c r="B17" s="49"/>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="41"/>
+      <c r="B17" s="41"/>
       <c r="C17" s="1" t="s">
         <v>62</v>
       </c>
@@ -3684,11 +3791,11 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="49" t="s">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="49" t="s">
+      <c r="B18" s="41" t="s">
         <v>59</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -3701,9 +3808,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="49"/>
-      <c r="B19" s="49"/>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="41"/>
+      <c r="B19" s="41"/>
       <c r="C19" s="1" t="s">
         <v>109</v>
       </c>
@@ -3714,9 +3821,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="49"/>
-      <c r="B20" s="49" t="s">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="41"/>
+      <c r="B20" s="41" t="s">
         <v>58</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -3726,9 +3833,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="49"/>
-      <c r="B21" s="49"/>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="41"/>
+      <c r="B21" s="41"/>
       <c r="C21" s="1" t="s">
         <v>109</v>
       </c>
@@ -3736,7 +3843,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>47</v>
       </c>
@@ -3752,17 +3859,12 @@
       <c r="E22" s="1">
         <v>40</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="G22" s="1" t="s">
         <v>115</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B20:B21"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="A2:A4"/>
@@ -3770,6 +3872,11 @@
     <mergeCell ref="B5:B9"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="A5:A11"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B20:B21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3777,86 +3884,90 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B5B8E9C-ED44-4025-8C06-7A8E6EF3F3CC}">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="15.7109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="3.85546875" style="40" customWidth="1"/>
-    <col min="10" max="11" width="9.140625" style="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="9" width="15.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="3.85546875" style="40" customWidth="1"/>
+    <col min="11" max="12" width="9.140625" style="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="C1" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="G1" s="49" t="s">
+      <c r="G1" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="H1" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="H1" s="49" t="s">
+      <c r="I1" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="J1" s="49" t="s">
+      <c r="K1" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49" t="s">
+      <c r="L1" s="41"/>
+      <c r="M1" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="M1" s="49" t="s">
+      <c r="N1" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="N1" s="49" t="s">
+      <c r="O1" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="O1" s="49" t="s">
+      <c r="P1" s="41" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="49"/>
-      <c r="B2" s="49"/>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="41"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="J2" s="1" t="s">
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="K2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49"/>
-      <c r="N2" s="49"/>
-      <c r="O2" s="49"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -3875,14 +3986,17 @@
       <c r="F3" s="1">
         <v>24</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G3" s="1">
+        <v>308</v>
+      </c>
+      <c r="H3" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="H3" s="1">
+      <c r="I3" s="1">
         <v>440</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -3901,14 +4015,14 @@
       <c r="F4" s="1">
         <v>17</v>
       </c>
-      <c r="G4" s="27" t="s">
+      <c r="H4" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
         <v>1800</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -3927,14 +4041,17 @@
       <c r="F5" s="1">
         <v>24</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="1">
+        <v>308</v>
+      </c>
+      <c r="H5" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <v>440</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>43</v>
       </c>
@@ -3953,28 +4070,28 @@
       <c r="F6" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="H6" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="J6" s="35">
+      <c r="I6" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K6" s="35">
         <v>20</v>
       </c>
-      <c r="K6" s="35">
+      <c r="L6" s="35">
         <v>32.200000000000003</v>
       </c>
-      <c r="L6" s="35">
+      <c r="M6" s="35">
         <v>5</v>
       </c>
-      <c r="M6" s="35">
+      <c r="N6" s="35">
         <v>10.5</v>
       </c>
-      <c r="N6" s="35"/>
       <c r="O6" s="35"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P6" s="35"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>48</v>
       </c>
@@ -3993,14 +4110,14 @@
       <c r="F7" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="H7" s="1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I7" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>114</v>
       </c>
@@ -4019,32 +4136,33 @@
       <c r="F8" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="H8" s="1" t="s">
         <v>94</v>
       </c>
+      <c r="I8" s="1" t="s">
+        <v>94</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="G1:G2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="E1:E2"/>
-    <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
     <mergeCell ref="F1:F2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="O1:O2"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="J1:K1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G3" r:id="rId1" xr:uid="{D40B1BD2-F826-4A33-8F0F-ACB54534C7E7}"/>
-    <hyperlink ref="G4" r:id="rId2" xr:uid="{16E43108-C78E-4F6A-9639-C208C8803CEC}"/>
-    <hyperlink ref="G5" r:id="rId3" xr:uid="{56E3FF70-07CE-4DDB-BD05-5189FAD64199}"/>
+    <hyperlink ref="H3" r:id="rId1" xr:uid="{D40B1BD2-F826-4A33-8F0F-ACB54534C7E7}"/>
+    <hyperlink ref="H4" r:id="rId2" xr:uid="{16E43108-C78E-4F6A-9639-C208C8803CEC}"/>
+    <hyperlink ref="H5" r:id="rId3" xr:uid="{56E3FF70-07CE-4DDB-BD05-5189FAD64199}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
